--- a/reports/relatorio_2026_05.xlsx
+++ b/reports/relatorio_2026_05.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
@@ -524,6 +524,30 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EDP - FATURAS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
